--- a/BOXApp%SC_1.xlsx
+++ b/BOXApp%SC_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\urjita\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3ED546-1603-4DA8-AF3E-35A509CFB390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7DDB66-3C2C-416B-AEE9-01E385D63178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -406,16 +406,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2F7064-A36A-4D42-B706-2A3F253C1352}">
-  <dimension ref="G15"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="15" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G15">
-        <f>45*693</f>
-        <v>31185</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/BOXApp%SC_1.xlsx
+++ b/BOXApp%SC_1.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\urjita\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7DDB66-3C2C-416B-AEE9-01E385D63178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908518F7-3327-4953-919A-03F32C3E9174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -405,15 +404,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2F7064-A36A-4D42-B706-2A3F253C1352}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{689B982D-FDA5-4059-9231-C9841120C17A}">
   <dimension ref="D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
